--- a/每日输出/高短/郑州-高短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/高短/郑州-高短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,7 +51,7 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="00C00000"/>
+      <color rgb="0000B050"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -61,14 +61,18 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="0000B050"/>
     </font>
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="0000B050"/>
+      <color rgb="00C00000"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -219,7 +223,7 @@
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -237,13 +241,13 @@
     <xf numFmtId="9" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9122,16 +9126,16 @@
         <v>8</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>0.875</v>
       </c>
     </row>
     <row r="4">
@@ -9155,16 +9159,16 @@
         <v>8</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>0.875</v>
       </c>
     </row>
     <row r="5">
@@ -9192,16 +9196,16 @@
         <v>10</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -9218,23 +9222,23 @@
       <c r="E6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="13" t="n">
         <v>0.2857142857142857</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>7</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="13" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="7">
@@ -9258,16 +9262,16 @@
         <v>10</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K7" s="14" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -9291,16 +9295,16 @@
         <v>27</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>0.07407407407407407</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>0.5</v>
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>0.4230769230769231</v>
       </c>
     </row>
     <row r="9">
@@ -9321,23 +9325,23 @@
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="13" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -9354,7 +9358,7 @@
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -9366,10 +9370,10 @@
       <c r="I10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="13" t="e">
+      <c r="K10" s="15" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -9387,23 +9391,23 @@
       <c r="E11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="14" t="n">
         <v>0.5</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>2</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="15" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -9424,23 +9428,23 @@
       <c r="E12" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="13" t="n">
         <v>0.3636363636363636</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0</v>
+      <c r="J12" s="8" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="13">
@@ -9457,23 +9461,23 @@
       <c r="E13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -9497,16 +9501,16 @@
         <v>9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K14" s="14" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="15">
@@ -9523,23 +9527,23 @@
       <c r="E15" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="13" t="n">
         <v>0.4736842105263158</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>19</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>0</v>
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="16">
@@ -9556,23 +9560,23 @@
       <c r="E16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="13" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -9589,23 +9593,23 @@
       <c r="E17" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="14" t="n">
         <v>0.4782608695652174</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>46</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>0.1304347826086956</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>0.1666666666666667</v>
+        <v>21</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>0.5121951219512195</v>
       </c>
     </row>
     <row r="18">
@@ -9626,23 +9630,23 @@
       <c r="E18" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="14" t="n">
         <v>0.5542168674698795</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>83</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>0.1204819277108434</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>0.3</v>
+        <v>0.9156626506024096</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>0.5263157894736842</v>
       </c>
     </row>
   </sheetData>
@@ -9694,58 +9698,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>学部</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>年级</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>战队</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>老师邮箱</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>老师姓名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>个微授权</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>整体正常</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>运营中心</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>日期</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9757,7 +9761,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9767,38 +9771,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>星火先锋-秦智豪</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>qinzhihao</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>秦智豪</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
       <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -9808,7 +9812,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9818,38 +9822,38 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>星火先锋-秦智豪</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>xiaochenglong</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>肖成龙</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>hemingchao</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>何明超</t>
+        </is>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
+      <c r="I3" t="n">
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -9859,7 +9863,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9869,38 +9873,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高短</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南征北战-张胜迪</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>zhangshengdi</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>张胜迪</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+          <t>hewenjing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>何雯静</t>
+        </is>
       </c>
       <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -9910,7 +9914,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9920,38 +9924,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高短</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>风禾尽起-陈春雨</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>liuchang05</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>刘畅</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>huojinpeng</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>霍金鹏</t>
+        </is>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -9961,7 +9965,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9971,38 +9975,38 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高短</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>gezengguang</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>葛增光</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>qinzhihao</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>秦智豪</t>
+        </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -10012,7 +10016,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10022,38 +10026,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高短</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>mengchenyang</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>孟晨阳</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>sunluping</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>孙鲁平</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -10063,7 +10067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10073,38 +10077,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高短</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>勇立潮头-王雅欣</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>wangyaxin</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>王雅欣</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
+          <t>wangjiamei</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>王佳美</t>
+        </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -10114,7 +10118,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -10124,38 +10128,38 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高短</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>所向披靡-刘振超</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sunhuanhuan</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>孙欢欢</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>xiaochenglong</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>肖成龙</t>
+        </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -10165,7 +10169,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10175,38 +10179,38 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高短</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>溯川向上-刘炎鹤</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>xushenghu</t>
+          <t>星火先锋-秦智豪</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>许圣虎</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>youzhenzhong</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>尤振中</t>
+        </is>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
+      <c r="I10" t="n">
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -10216,7 +10220,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10226,38 +10230,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高短</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>青云折桂-彭铖名</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>niuhehe</t>
+          <t>南征北战-张胜迪</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>牛禾禾</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>fandongcheng</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>凡栋程</t>
+        </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -10267,7 +10271,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>高短</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10277,41 +10281,3713 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高短</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>南征北战-张胜迪</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>limengping</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>李梦萍</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>南征北战-张胜迪</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>liuyirun</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>刘一润</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>南征北战-张胜迪</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>wanghongzhe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>王宏哲</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>南征北战-张胜迪</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>wuhuijuan</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>吴慧娟</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>南征北战-张胜迪</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>yangfan03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>杨帆</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>南征北战-张胜迪</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>zhanglinxin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>张琳鑫</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>南征北战-张胜迪</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>zhangqianqian03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>张芊芊</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>南征北战-张胜迪</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>zhangshengdi</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>张胜迪</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>南征北战-张胜迪</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zhangzuo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>张作</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>追求卓越-白志勇</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>baizhiyong</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>白志勇</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>追求卓越-白志勇</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>chenruiyang</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>陈瑞阳</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>追求卓越-白志勇</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>cuichengjie</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>崔成杰</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>追求卓越-白志勇</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>mayuhan</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>马雨菡</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>追求卓越-白志勇</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>wangsen</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>王森</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>追求卓越-白志勇</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>wangzhibo</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>王智博</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>追求卓越-白志勇</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>yuhai</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>余海</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>caowenhao</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>曹文浩</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>chenchunyu</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>陈春雨</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>lidongbo</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>李东博</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>lilin01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>李琳</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>liuchang05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>刘畅</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>liupeihao</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>刘培豪</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>lixinyi</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>李欣怡</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>qinyingying</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>秦盈盈</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>weijunjie</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>魏君杰</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>风禾尽起-陈春雨</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>xingruoxiang</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>邢若湘</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>凌云壮志-张海升</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>mudoudou</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>穆豆豆</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>同心致远-宋长金</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>zhangyu</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>张宇</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>dongzhe</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>董哲</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>gezengguang</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>葛增光</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>kongmiaomiao</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>孔苗苗</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>libingshuo01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>李兵硕</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>liqiaorui</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>李巧瑞</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>lixianfu</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>李显福</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>mengchenyang</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>孟晨阳</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>qiaoshuhan</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>乔淑涵</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>songyiqing</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>宋义庆</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>wangyaxin</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>王雅欣</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>勇立潮头-王雅欣</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>zhangli</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>张丽</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>所向披靡-刘振超</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>jiamenghui</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>贾梦辉</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>所向披靡-刘振超</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>liuzhenchao</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>刘振超</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>所向披靡-刘振超</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>qimiaomiao</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>齐苗苗</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>所向披靡-刘振超</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>songhaiyan</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>宋海燕</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>所向披靡-刘振超</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>sunhuanhuan</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>孙欢欢</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>所向披靡-刘振超</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>zhuliuwei</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>朱六威</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>溯川向上-刘炎鹤</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>fanchunyan</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>范春艳</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>溯川向上-刘炎鹤</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>gaochong</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>高冲</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>溯川向上-刘炎鹤</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>jiaqiang</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>贾强</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>溯川向上-刘炎鹤</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>liuchuanbo</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>刘传波</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>溯川向上-刘炎鹤</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>liuyanhe</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>刘炎鹤</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>溯川向上-刘炎鹤</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>shangjunyi</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>尚俊逸</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>溯川向上-刘炎鹤</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>xushenghu</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>许圣虎</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>溯川向上-刘炎鹤</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>yangjingyu</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>杨靖宇</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>溯川向上-刘炎鹤</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>yuxiang</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>于香</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>青云折桂-彭铖名</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>fanyuqin</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>范玉琴</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>fengkehao</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>冯科皓</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>hanjiabao</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>韩家宝</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>lidihao</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>李迪豪</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>lijiawei02</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>李嘉威</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>liuzhen01</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>刘振</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>lizhiyuan01</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>李志远</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>niuhehe</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>牛禾禾</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>pengchengming</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>彭铖名</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>qiyingzheng</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>祁赢政</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>sunxinyu01</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>孙欣雨</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>wangzhaoxi</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>王照玺</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>yanghualong</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>杨化龙</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>yanglongxiang</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>杨龙祥</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>zhangchen01</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>张晨</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>郑州</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>zhangyinlong01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>张银龙</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>zhongyi</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>钟毅</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>青云折桂-彭铖名</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>zhucaoyuan</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>朱草原</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>鼎立苍穹-吕萍</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>gaokai</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>高凯</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
         <v>22</v>
       </c>
     </row>
@@ -10391,16 +14067,16 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="3">
@@ -10423,16 +14099,16 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -10455,13 +14131,16 @@
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="5">
@@ -10484,16 +14163,16 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
@@ -10516,13 +14195,16 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -10574,16 +14256,16 @@
         <v>11</v>
       </c>
       <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -10606,16 +14288,16 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -10638,16 +14320,16 @@
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1111111111111111</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="11">
@@ -10670,16 +14352,16 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="12">
@@ -10702,13 +14384,16 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
